--- a/data/trans_orig/P19C02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76512</t>
+          <t>75581</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110456</t>
+          <t>108180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92194</t>
+          <t>92451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125175</t>
+          <t>125810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177096</t>
+          <t>178851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225221</t>
+          <t>226021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248945</t>
+          <t>251221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282889</t>
+          <t>283820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251077</t>
+          <t>250442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284058</t>
+          <t>283801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510432</t>
+          <t>509632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>558557</t>
+          <t>556802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202110</t>
+          <t>202410</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>249038</t>
+          <t>250510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>188260</t>
+          <t>186438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>232609</t>
+          <t>232733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>399485</t>
+          <t>398954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>465827</t>
+          <t>464453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>326743</t>
+          <t>325271</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373671</t>
+          <t>373371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314118</t>
+          <t>313994</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358467</t>
+          <t>360289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>656681</t>
+          <t>658055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723023</t>
+          <t>723554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160286</t>
+          <t>160469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205248</t>
+          <t>202339</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183444</t>
+          <t>181398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>230795</t>
+          <t>230269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>353118</t>
+          <t>354567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>419355</t>
+          <t>417328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297685</t>
+          <t>300594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>342647</t>
+          <t>342464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>372770</t>
+          <t>373296</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>420121</t>
+          <t>422167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>687142</t>
+          <t>689169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>753379</t>
+          <t>751930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106673</t>
+          <t>104730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>143905</t>
+          <t>144801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120708</t>
+          <t>122963</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159972</t>
+          <t>162552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242228</t>
+          <t>240765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>293334</t>
+          <t>295094</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260843</t>
+          <t>259947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298075</t>
+          <t>300018</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>278197</t>
+          <t>275617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317461</t>
+          <t>315206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>549583</t>
+          <t>547823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>600689</t>
+          <t>602152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41286</t>
+          <t>40240</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66759</t>
+          <t>66577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65295</t>
+          <t>64845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95961</t>
+          <t>95461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112548</t>
+          <t>113182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151791</t>
+          <t>154070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205590</t>
+          <t>205772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>231063</t>
+          <t>232109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223121</t>
+          <t>223621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>253787</t>
+          <t>254237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>439640</t>
+          <t>437361</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>478883</t>
+          <t>478249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13890</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>31307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33336</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>55616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49847</t>
+          <t>49968</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79375</t>
+          <t>78806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181968</t>
+          <t>181458</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198875</t>
+          <t>198972</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>190031</t>
+          <t>190391</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212671</t>
+          <t>212406</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>379397</t>
+          <t>379966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>408925</t>
+          <t>408804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9625</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>27445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114336</t>
+          <t>113275</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124146</t>
+          <t>124130</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188367</t>
+          <t>189837</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>203553</t>
+          <t>202840</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>308840</t>
+          <t>307527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>325243</t>
+          <t>325347</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>660275</t>
+          <t>658676</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>751819</t>
+          <t>746373</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>754103</t>
+          <t>747514</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>843476</t>
+          <t>844575</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1431757</t>
+          <t>1434830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1566168</t>
+          <t>1562899</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1702923</t>
+          <t>1708369</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1794467</t>
+          <t>1796066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1894533</t>
+          <t>1893434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1983906</t>
+          <t>1990495</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3626582</t>
+          <t>3629851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3760993</t>
+          <t>3757920</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72028</t>
+          <t>74052</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105197</t>
+          <t>106347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83227</t>
+          <t>80267</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116976</t>
+          <t>115035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>162828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212984</t>
+          <t>210132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273979</t>
+          <t>272829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307148</t>
+          <t>305124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254015</t>
+          <t>255956</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287764</t>
+          <t>290724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537182</t>
+          <t>540034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586112</t>
+          <t>587338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,29%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>192819</t>
+          <t>190779</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>239322</t>
+          <t>239884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>177777</t>
+          <t>180443</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>223680</t>
+          <t>229690</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>386543</t>
+          <t>384224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>454014</t>
+          <t>451155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357945</t>
+          <t>357383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404448</t>
+          <t>406488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336171</t>
+          <t>330161</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>382074</t>
+          <t>379408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703104</t>
+          <t>705963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>770575</t>
+          <t>772894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203352</t>
+          <t>201958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>251657</t>
+          <t>250305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>232335</t>
+          <t>234210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>284568</t>
+          <t>285625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>453861</t>
+          <t>454245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>524297</t>
+          <t>524479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>334994</t>
+          <t>336346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>383299</t>
+          <t>384693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>375824</t>
+          <t>374767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>428057</t>
+          <t>426182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>722746</t>
+          <t>722564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>793182</t>
+          <t>792798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161059</t>
+          <t>159813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209215</t>
+          <t>209366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>193444</t>
+          <t>195443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243048</t>
+          <t>245140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>371469</t>
+          <t>369746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>438196</t>
+          <t>437329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333624</t>
+          <t>333473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>381780</t>
+          <t>383026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320303</t>
+          <t>318211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369907</t>
+          <t>367908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667994</t>
+          <t>668861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734721</t>
+          <t>736444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68629</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101784</t>
+          <t>101536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92414</t>
+          <t>93831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131809</t>
+          <t>132909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172918</t>
+          <t>173969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>222930</t>
+          <t>224804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257465</t>
+          <t>257713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>290620</t>
+          <t>290710</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>258906</t>
+          <t>257806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>298301</t>
+          <t>296884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>527035</t>
+          <t>525161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>577047</t>
+          <t>575996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23974</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48009</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42303</t>
+          <t>40982</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69409</t>
+          <t>68979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72651</t>
+          <t>73500</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109123</t>
+          <t>109735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213489</t>
+          <t>213740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237524</t>
+          <t>236478</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231180</t>
+          <t>231610</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258286</t>
+          <t>259607</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>452964</t>
+          <t>452352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>489436</t>
+          <t>488587</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39970</t>
+          <t>38245</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25157</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48786</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47938</t>
+          <t>48728</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80954</t>
+          <t>79292</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>144956</t>
+          <t>146681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167072</t>
+          <t>167280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>253627</t>
+          <t>254920</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>277256</t>
+          <t>278490</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>406385</t>
+          <t>408047</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>439401</t>
+          <t>438611</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>810594</t>
+          <t>813097</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>914182</t>
+          <t>915239</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>935900</t>
+          <t>924557</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1040413</t>
+          <t>1035890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1782601</t>
+          <t>1772288</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1927511</t>
+          <t>1921758</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1997424</t>
+          <t>1996367</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2101012</t>
+          <t>2098509</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2107889</t>
+          <t>2112412</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2212402</t>
+          <t>2223745</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4132397</t>
+          <t>4138150</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4277307</t>
+          <t>4287620</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100924</t>
+          <t>101133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137421</t>
+          <t>137942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102583</t>
+          <t>101916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136936</t>
+          <t>135806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213673</t>
+          <t>210343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>264872</t>
+          <t>259729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215419</t>
+          <t>214898</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251916</t>
+          <t>251707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214994</t>
+          <t>216124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249347</t>
+          <t>250014</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>439898</t>
+          <t>445041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>491097</t>
+          <t>494427</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179262</t>
+          <t>177807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223793</t>
+          <t>221126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169617</t>
+          <t>168291</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210616</t>
+          <t>210690</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359243</t>
+          <t>360008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>419134</t>
+          <t>418347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>269285</t>
+          <t>271952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313816</t>
+          <t>315271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286104</t>
+          <t>286030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327103</t>
+          <t>328429</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>570663</t>
+          <t>571450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>630554</t>
+          <t>629789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,63%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>212508</t>
+          <t>214357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>259549</t>
+          <t>259796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>230271</t>
+          <t>233792</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>276936</t>
+          <t>279656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>457602</t>
+          <t>458197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>525192</t>
+          <t>524301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298311</t>
+          <t>298064</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>345352</t>
+          <t>343503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296144</t>
+          <t>293424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>342809</t>
+          <t>339288</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>605748</t>
+          <t>606639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673338</t>
+          <t>672743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>168118</t>
+          <t>169679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>213959</t>
+          <t>215639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>215254</t>
+          <t>216894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263574</t>
+          <t>264767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>399551</t>
+          <t>396772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>464163</t>
+          <t>466412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298413</t>
+          <t>296733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>344254</t>
+          <t>342693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281310</t>
+          <t>280117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>329630</t>
+          <t>327990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>593093</t>
+          <t>590844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>657705</t>
+          <t>660484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86908</t>
+          <t>88399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123963</t>
+          <t>123949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119457</t>
+          <t>117015</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159277</t>
+          <t>157249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214751</t>
+          <t>213857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269191</t>
+          <t>270187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>247039</t>
+          <t>247053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>284094</t>
+          <t>282603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>236596</t>
+          <t>238624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>276416</t>
+          <t>278858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>497684</t>
+          <t>496688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>552124</t>
+          <t>553018</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36836</t>
+          <t>39476</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62661</t>
+          <t>64202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67300</t>
+          <t>68232</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99398</t>
+          <t>99404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112738</t>
+          <t>114083</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152246</t>
+          <t>154011</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167464</t>
+          <t>165923</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193289</t>
+          <t>190649</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177550</t>
+          <t>177544</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209648</t>
+          <t>208716</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>354828</t>
+          <t>353063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>394336</t>
+          <t>392991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38436</t>
+          <t>37664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>31429</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60271</t>
+          <t>59689</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58007</t>
+          <t>57597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89500</t>
+          <t>90335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108621</t>
+          <t>109393</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126548</t>
+          <t>127056</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>167608</t>
+          <t>168190</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>194789</t>
+          <t>196450</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>285436</t>
+          <t>284601</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>316929</t>
+          <t>317339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>879600</t>
+          <t>877134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>976764</t>
+          <t>974335</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1009448</t>
+          <t>1011762</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1119982</t>
+          <t>1112294</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1919510</t>
+          <t>1924967</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2064428</t>
+          <t>2070108</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1687569</t>
+          <t>1689998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1784733</t>
+          <t>1787199</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1747333</t>
+          <t>1755021</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1857867</t>
+          <t>1855553</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3467220</t>
+          <t>3461540</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3612138</t>
+          <t>3606681</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>137293</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>209030</t>
+          <t>205678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96157</t>
+          <t>95850</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138662</t>
+          <t>141132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>250116</t>
+          <t>247514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>330831</t>
+          <t>329890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174417</t>
+          <t>177769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242735</t>
+          <t>246154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164879</t>
+          <t>162409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207384</t>
+          <t>207691</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>356157</t>
+          <t>357098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436872</t>
+          <t>439474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,97%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195673</t>
+          <t>196655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>246561</t>
+          <t>250587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154082</t>
+          <t>145206</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>277863</t>
+          <t>279558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>357674</t>
+          <t>360700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>507973</t>
+          <t>508194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155790</t>
+          <t>151764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206678</t>
+          <t>205696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221829</t>
+          <t>220134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345610</t>
+          <t>354486</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>394069</t>
+          <t>393848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>544368</t>
+          <t>541342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>271483</t>
+          <t>270683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>317915</t>
+          <t>317776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>283846</t>
+          <t>282735</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>321613</t>
+          <t>321021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>565502</t>
+          <t>565166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627649</t>
+          <t>627324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206127</t>
+          <t>206266</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>252559</t>
+          <t>253359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210268</t>
+          <t>210860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248035</t>
+          <t>249146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>428274</t>
+          <t>428599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>490421</t>
+          <t>490757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,48%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134581</t>
+          <t>136262</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>443711</t>
+          <t>442577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>297472</t>
+          <t>310236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>390973</t>
+          <t>390859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>407307</t>
+          <t>382575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>813829</t>
+          <t>816955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>418251</t>
+          <t>419385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>727381</t>
+          <t>725700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309619</t>
+          <t>309733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>403120</t>
+          <t>390356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748725</t>
+          <t>745599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1155247</t>
+          <t>1179979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>227909</t>
+          <t>229124</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>271211</t>
+          <t>272588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>255708</t>
+          <t>256545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>290145</t>
+          <t>291222</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>498272</t>
+          <t>495619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>551692</t>
+          <t>551205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>275368</t>
+          <t>273991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>318670</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>244381</t>
+          <t>243304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>278818</t>
+          <t>277981</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>529413</t>
+          <t>529900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>582833</t>
+          <t>585486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>125764</t>
+          <t>126368</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>156187</t>
+          <t>156333</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>254605</t>
+          <t>252019</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>514749</t>
+          <t>506044</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>388894</t>
+          <t>390357</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>729934</t>
+          <t>727165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>203166</t>
+          <t>203020</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233589</t>
+          <t>232985</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85160</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>345304</t>
+          <t>347890</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>229328</t>
+          <t>232097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>570368</t>
+          <t>568905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58930</t>
+          <t>60051</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82807</t>
+          <t>82434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105510</t>
+          <t>104674</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131243</t>
+          <t>130562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>170393</t>
+          <t>171936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206437</t>
+          <t>206843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193419</t>
+          <t>193792</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217296</t>
+          <t>216175</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277444</t>
+          <t>278125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>303177</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478476</t>
+          <t>478070</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>514520</t>
+          <t>512977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1134610</t>
+          <t>1140942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1595896</t>
+          <t>1588859</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1646831</t>
+          <t>1639898</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2130632</t>
+          <t>2089353</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2905594</t>
+          <t>2925284</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3533389</t>
+          <t>3527322</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1758064</t>
+          <t>1765101</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2219350</t>
+          <t>2213018</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1448195</t>
+          <t>1489474</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1931996</t>
+          <t>1938929</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3399398</t>
+          <t>3405465</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4027193</t>
+          <t>4007503</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75581</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108180</t>
+          <t>111100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92451</t>
+          <t>92337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125810</t>
+          <t>127734</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178851</t>
+          <t>177988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>226021</t>
+          <t>225393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251221</t>
+          <t>248301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283820</t>
+          <t>282208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250442</t>
+          <t>248518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283801</t>
+          <t>283915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>509632</t>
+          <t>510260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>556802</t>
+          <t>557665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202410</t>
+          <t>200974</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250510</t>
+          <t>248843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186438</t>
+          <t>185872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>232733</t>
+          <t>232227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>398954</t>
+          <t>402568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>464453</t>
+          <t>466663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325271</t>
+          <t>326938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373371</t>
+          <t>374807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313994</t>
+          <t>314500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360289</t>
+          <t>360855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658055</t>
+          <t>655845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723554</t>
+          <t>719940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160469</t>
+          <t>160654</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202339</t>
+          <t>203206</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>181398</t>
+          <t>181801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>230269</t>
+          <t>227025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>354567</t>
+          <t>354501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>417328</t>
+          <t>421633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300594</t>
+          <t>299727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>342464</t>
+          <t>342279</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>373296</t>
+          <t>376540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>422167</t>
+          <t>421764</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>689169</t>
+          <t>684864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>751930</t>
+          <t>751996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104730</t>
+          <t>106722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144801</t>
+          <t>145358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122963</t>
+          <t>122133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162552</t>
+          <t>160564</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>240765</t>
+          <t>238003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295094</t>
+          <t>294812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259947</t>
+          <t>259390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300018</t>
+          <t>298026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275617</t>
+          <t>277605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315206</t>
+          <t>316036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>547823</t>
+          <t>548105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>602152</t>
+          <t>604914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40240</t>
+          <t>40439</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66577</t>
+          <t>66385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64845</t>
+          <t>66719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95461</t>
+          <t>96542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113182</t>
+          <t>111635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154070</t>
+          <t>152050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205772</t>
+          <t>205964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>232109</t>
+          <t>231910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223621</t>
+          <t>222540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254237</t>
+          <t>252363</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>437361</t>
+          <t>439381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>478249</t>
+          <t>479796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31307</t>
+          <t>30879</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55616</t>
+          <t>56089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49968</t>
+          <t>51553</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78806</t>
+          <t>80165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181458</t>
+          <t>181886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198972</t>
+          <t>199501</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>190391</t>
+          <t>189918</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212406</t>
+          <t>213341</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>379966</t>
+          <t>378607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>408804</t>
+          <t>407219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9625</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27445</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113275</t>
+          <t>114032</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124130</t>
+          <t>124431</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>189837</t>
+          <t>188633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>202840</t>
+          <t>203487</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>307527</t>
+          <t>307970</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>325347</t>
+          <t>325703</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>658676</t>
+          <t>659841</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>746373</t>
+          <t>748681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>747514</t>
+          <t>752463</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>844575</t>
+          <t>845461</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1434830</t>
+          <t>1433902</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1562899</t>
+          <t>1560556</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1708369</t>
+          <t>1706061</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1796066</t>
+          <t>1794901</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1893434</t>
+          <t>1892548</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1990495</t>
+          <t>1985546</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3629851</t>
+          <t>3632194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3757920</t>
+          <t>3758848</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74052</t>
+          <t>71710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106347</t>
+          <t>104956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80267</t>
+          <t>79929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115035</t>
+          <t>115002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>162828</t>
+          <t>162795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210132</t>
+          <t>210485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272829</t>
+          <t>274220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305124</t>
+          <t>307466</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255956</t>
+          <t>255989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290724</t>
+          <t>291062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540034</t>
+          <t>539681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587338</t>
+          <t>587371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>190779</t>
+          <t>190965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>239884</t>
+          <t>240548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180443</t>
+          <t>179693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229690</t>
+          <t>226757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>384224</t>
+          <t>382089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>451155</t>
+          <t>451990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357383</t>
+          <t>356719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>406488</t>
+          <t>406302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330161</t>
+          <t>333094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379408</t>
+          <t>380158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705963</t>
+          <t>705128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>772894</t>
+          <t>775029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,98%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>201958</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>250305</t>
+          <t>254552</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>234210</t>
+          <t>236281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>285625</t>
+          <t>287111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>454245</t>
+          <t>454433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>524479</t>
+          <t>521139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>336346</t>
+          <t>332099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>384693</t>
+          <t>382963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>374767</t>
+          <t>373281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>426182</t>
+          <t>424111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>722564</t>
+          <t>725904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>792798</t>
+          <t>792610</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,56%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159813</t>
+          <t>161458</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209366</t>
+          <t>208131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195443</t>
+          <t>193322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245140</t>
+          <t>242858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369746</t>
+          <t>370042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>437329</t>
+          <t>438952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333473</t>
+          <t>334708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>383026</t>
+          <t>381381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>318211</t>
+          <t>320493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367908</t>
+          <t>370029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>668861</t>
+          <t>667238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>736444</t>
+          <t>736148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,55%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68539</t>
+          <t>69746</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101536</t>
+          <t>102283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>93831</t>
+          <t>95067</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132909</t>
+          <t>132841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>173969</t>
+          <t>172602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224804</t>
+          <t>222463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257713</t>
+          <t>256966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>290710</t>
+          <t>289503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>257806</t>
+          <t>257874</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>296884</t>
+          <t>295648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>525161</t>
+          <t>527502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>575996</t>
+          <t>577363</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25020</t>
+          <t>24345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47758</t>
+          <t>48416</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40982</t>
+          <t>42132</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68979</t>
+          <t>69138</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73500</t>
+          <t>73436</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109735</t>
+          <t>108136</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213740</t>
+          <t>213082</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236478</t>
+          <t>237153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231610</t>
+          <t>231451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259607</t>
+          <t>258457</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>452352</t>
+          <t>453951</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>488587</t>
+          <t>488651</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38245</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23923</t>
+          <t>25811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>48532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>48018</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79292</t>
+          <t>77844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146681</t>
+          <t>146946</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167280</t>
+          <t>166612</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>254920</t>
+          <t>253881</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>278490</t>
+          <t>276602</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408047</t>
+          <t>409495</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>438611</t>
+          <t>439321</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>813097</t>
+          <t>810338</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>915239</t>
+          <t>915626</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>924557</t>
+          <t>925666</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1035890</t>
+          <t>1036465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1772288</t>
+          <t>1778019</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1921758</t>
+          <t>1922867</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1996367</t>
+          <t>1995980</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2098509</t>
+          <t>2101268</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2112412</t>
+          <t>2111837</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2223745</t>
+          <t>2222636</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4138150</t>
+          <t>4137041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4287620</t>
+          <t>4281889</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,66%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101133</t>
+          <t>99495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>136219</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101916</t>
+          <t>101287</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135806</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>210343</t>
+          <t>210565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>259729</t>
+          <t>261239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214898</t>
+          <t>216621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251707</t>
+          <t>253345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216124</t>
+          <t>216778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250014</t>
+          <t>250643</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>445041</t>
+          <t>443531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>494427</t>
+          <t>494205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177807</t>
+          <t>178728</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221126</t>
+          <t>220972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168291</t>
+          <t>169469</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210690</t>
+          <t>210468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>360008</t>
+          <t>359603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>418347</t>
+          <t>419102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271952</t>
+          <t>272106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>315271</t>
+          <t>314350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286030</t>
+          <t>286252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328429</t>
+          <t>327251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>571450</t>
+          <t>570695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>629789</t>
+          <t>630194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214357</t>
+          <t>212889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>259796</t>
+          <t>261117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>233792</t>
+          <t>233518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>279656</t>
+          <t>278436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>458197</t>
+          <t>458812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>524301</t>
+          <t>527547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298064</t>
+          <t>296743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343503</t>
+          <t>344971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293424</t>
+          <t>294644</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339288</t>
+          <t>339562</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>606639</t>
+          <t>603393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>672743</t>
+          <t>672128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169679</t>
+          <t>170970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215639</t>
+          <t>215341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216894</t>
+          <t>214887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>264767</t>
+          <t>262467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>396772</t>
+          <t>399339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>466412</t>
+          <t>462580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296733</t>
+          <t>297031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342693</t>
+          <t>341402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>280117</t>
+          <t>282417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>327990</t>
+          <t>329997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>590844</t>
+          <t>594676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>660484</t>
+          <t>657917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88399</t>
+          <t>87721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123949</t>
+          <t>125342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117015</t>
+          <t>117432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157249</t>
+          <t>156304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213857</t>
+          <t>214266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>270187</t>
+          <t>270069</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>247053</t>
+          <t>245660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282603</t>
+          <t>283281</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>238624</t>
+          <t>239569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>278858</t>
+          <t>278441</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>496688</t>
+          <t>496806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>553018</t>
+          <t>552609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39476</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64202</t>
+          <t>63383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68232</t>
+          <t>65596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99404</t>
+          <t>97282</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114083</t>
+          <t>113555</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154011</t>
+          <t>152694</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165923</t>
+          <t>166742</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190649</t>
+          <t>191381</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177544</t>
+          <t>179666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208716</t>
+          <t>211352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>353063</t>
+          <t>354380</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>392991</t>
+          <t>393519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>38385</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31429</t>
+          <t>32476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59689</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57597</t>
+          <t>58172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90335</t>
+          <t>88766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109393</t>
+          <t>108672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127056</t>
+          <t>126522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>168190</t>
+          <t>169910</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>196450</t>
+          <t>195403</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>284601</t>
+          <t>286170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>317339</t>
+          <t>316764</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>877134</t>
+          <t>878313</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>974335</t>
+          <t>979996</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1011762</t>
+          <t>1011202</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1112294</t>
+          <t>1118218</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1924967</t>
+          <t>1924204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2070108</t>
+          <t>2069709</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1689998</t>
+          <t>1684337</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1787199</t>
+          <t>1786020</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1755021</t>
+          <t>1749097</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1855553</t>
+          <t>1856113</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3461540</t>
+          <t>3461939</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3606681</t>
+          <t>3607444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>171977</t>
+          <t>170139</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137293</t>
+          <t>139002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205678</t>
+          <t>200897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>116932</t>
+          <t>144522</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95850</t>
+          <t>122534</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141132</t>
+          <t>169568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>288909</t>
+          <t>314661</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247514</t>
+          <t>273234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>329890</t>
+          <t>351755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>211470</t>
+          <t>208715</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>177769</t>
+          <t>177957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246154</t>
+          <t>239852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>186609</t>
+          <t>198718</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162409</t>
+          <t>173672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207691</t>
+          <t>220706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>398079</t>
+          <t>407433</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>357098</t>
+          <t>370339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>439474</t>
+          <t>448860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>222667</t>
+          <t>249887</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>196655</t>
+          <t>220778</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250587</t>
+          <t>276443</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>232506</t>
+          <t>260120</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145206</t>
+          <t>234863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>279558</t>
+          <t>281070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>455173</t>
+          <t>510007</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>360700</t>
+          <t>475927</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>508194</t>
+          <t>542809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179684</t>
+          <t>196006</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151764</t>
+          <t>169450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>205696</t>
+          <t>225115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>267186</t>
+          <t>222489</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220134</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354486</t>
+          <t>247746</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>446869</t>
+          <t>418495</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>393848</t>
+          <t>385693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>541342</t>
+          <t>452575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>294726</t>
+          <t>329066</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>270683</t>
+          <t>302004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>317776</t>
+          <t>353186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>302627</t>
+          <t>341049</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>282735</t>
+          <t>321043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>321021</t>
+          <t>361712</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>597354</t>
+          <t>670114</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>565166</t>
+          <t>632658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627324</t>
+          <t>704141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,27%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>229316</t>
+          <t>272058</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206266</t>
+          <t>247938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253359</t>
+          <t>299120</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>229254</t>
+          <t>266233</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210860</t>
+          <t>245570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>249146</t>
+          <t>286239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>458569</t>
+          <t>538291</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>428599</t>
+          <t>504264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>490757</t>
+          <t>575747</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>309573</t>
+          <t>338762</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136262</t>
+          <t>310887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>442577</t>
+          <t>363838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>362261</t>
+          <t>392262</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310236</t>
+          <t>368169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>390859</t>
+          <t>411470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>671833</t>
+          <t>731024</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>382575</t>
+          <t>694152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>816955</t>
+          <t>761758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>552389</t>
+          <t>338615</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>419385</t>
+          <t>313539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>725700</t>
+          <t>366490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>338331</t>
+          <t>329495</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309733</t>
+          <t>310287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>390356</t>
+          <t>353588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>890721</t>
+          <t>668109</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>745599</t>
+          <t>637375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1179979</t>
+          <t>704981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>861962</t>
+          <t>677377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>861962</t>
+          <t>677377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>861962</t>
+          <t>677377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1562554</t>
+          <t>1399133</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1562554</t>
+          <t>1399133</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1562554</t>
+          <t>1399133</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>249555</t>
+          <t>273933</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229124</t>
+          <t>250781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>272588</t>
+          <t>298354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>274325</t>
+          <t>306476</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>256545</t>
+          <t>285777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>291222</t>
+          <t>323342</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>523881</t>
+          <t>580409</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>495619</t>
+          <t>552003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>551205</t>
+          <t>609698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>297024</t>
+          <t>319422</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>273991</t>
+          <t>295001</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>317455</t>
+          <t>342574</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>260201</t>
+          <t>289373</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>243304</t>
+          <t>272507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>277981</t>
+          <t>310072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>557224</t>
+          <t>608795</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>529900</t>
+          <t>579506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>585486</t>
+          <t>637201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>141190</t>
+          <t>161130</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126368</t>
+          <t>144517</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>156333</t>
+          <t>178081</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>376215</t>
+          <t>187807</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>252019</t>
+          <t>173060</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>506044</t>
+          <t>202652</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>517405</t>
+          <t>348937</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>390357</t>
+          <t>326819</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>727165</t>
+          <t>371553</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>218163</t>
+          <t>236614</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>203020</t>
+          <t>219663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232985</t>
+          <t>253227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>223694</t>
+          <t>241118</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93865</t>
+          <t>226273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347890</t>
+          <t>255865</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>441857</t>
+          <t>477732</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>232097</t>
+          <t>455116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>568905</t>
+          <t>499850</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>70926</t>
+          <t>79349</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60051</t>
+          <t>66623</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82434</t>
+          <t>91806</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,67 +11758,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>117344</t>
+          <t>131329</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104674</t>
+          <t>117013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130562</t>
+          <t>147281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>26,25%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>33,04%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>210678</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>191824</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>229244</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>28,12%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>25,61%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>188270</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>171936</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>206843</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>27,49%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>205300</t>
+          <t>224012</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193792</t>
+          <t>211555</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>216175</t>
+          <t>236738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,67 +11871,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>291343</t>
+          <t>314457</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>278125</t>
+          <t>298505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>328773</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>73,75%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>538469</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>519903</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>557323</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>71,88%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>69,4%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>74,39%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>496643</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>478070</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>512977</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>72,51%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>69,8%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>276226</t>
+          <t>303361</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>276226</t>
+          <t>303361</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>276226</t>
+          <t>303361</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>684913</t>
+          <t>749147</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684913</t>
+          <t>749147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>684913</t>
+          <t>749147</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1460614</t>
+          <t>1602266</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1140942</t>
+          <t>1534252</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1588859</t>
+          <t>1669016</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1782210</t>
+          <t>1763564</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1639898</t>
+          <t>1713086</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2089353</t>
+          <t>1816654</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3242824</t>
+          <t>3365829</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2925284</t>
+          <t>3272423</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3527322</t>
+          <t>3448444</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1893346</t>
+          <t>1795441</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1765101</t>
+          <t>1728691</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2213018</t>
+          <t>1863455</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1796617</t>
+          <t>1861884</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1489474</t>
+          <t>1808794</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1938929</t>
+          <t>1912362</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3689963</t>
+          <t>3657326</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3405465</t>
+          <t>3574711</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4007503</t>
+          <t>3750732</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3353960</t>
+          <t>3397707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3353960</t>
+          <t>3397707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3353960</t>
+          <t>3397707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6932787</t>
+          <t>7023155</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6932787</t>
+          <t>7023155</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6932787</t>
+          <t>7023155</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
